--- a/data/trans_orig/P37B_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P37B_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el motivo por el que NO se vacunaron de la gripe en 2023</t>
+          <t>Población según el motivo por el que NO se vacunaron de la gripe en 2023 (tasa de respuesta: 97,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24616</t>
+          <t>24047</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50436</t>
+          <t>48450</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26047</t>
+          <t>26606</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46370</t>
+          <t>47003</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56265</t>
+          <t>56081</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88214</t>
+          <t>88022</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,97%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>531</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4789</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>534</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4674</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10601</t>
+          <t>10163</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26160</t>
+          <t>27187</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15044</t>
+          <t>15377</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17039</t>
+          <t>18422</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35178</t>
+          <t>36979</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>220081</t>
+          <t>221731</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>253124</t>
+          <t>252575</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>202533</t>
+          <t>202774</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>226927</t>
+          <t>226824</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>430615</t>
+          <t>430389</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>470969</t>
+          <t>471279</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,14%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11739</t>
+          <t>11408</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30536</t>
+          <t>30015</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12380</t>
+          <t>12549</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24952</t>
+          <t>25528</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26985</t>
+          <t>27849</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>50777</t>
+          <t>49724</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16802</t>
+          <t>16594</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38559</t>
+          <t>38668</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16120</t>
+          <t>16631</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31943</t>
+          <t>32572</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37372</t>
+          <t>37674</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63518</t>
+          <t>65694</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>928</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6557</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>933</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2991</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15331</t>
+          <t>14097</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14582</t>
+          <t>14527</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8760</t>
+          <t>8539</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23122</t>
+          <t>23722</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>202808</t>
+          <t>202211</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>231318</t>
+          <t>231401</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>197517</t>
+          <t>197780</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>219801</t>
+          <t>218591</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>409694</t>
+          <t>411016</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>446929</t>
+          <t>446105</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,23%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17063</t>
+          <t>17132</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35056</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11037</t>
+          <t>10691</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24570</t>
+          <t>23440</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31572</t>
+          <t>31682</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54727</t>
+          <t>55473</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41826</t>
+          <t>39189</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>454918</t>
+          <t>437753</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>17316</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52314</t>
+          <t>54467</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>502181</t>
+          <t>503900</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,68%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8415</t>
+          <t>8971</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>626</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>478</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13149</t>
+          <t>13462</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9267</t>
+          <t>9072</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2253</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19182</t>
+          <t>18914</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>66245</t>
+          <t>81064</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>436008</t>
+          <t>435551</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>63956</t>
+          <t>64460</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79339</t>
+          <t>79112</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>101863</t>
+          <t>103912</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>502849</t>
+          <t>501982</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,37%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41439</t>
+          <t>43923</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5891</t>
+          <t>5444</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14910</t>
+          <t>14483</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10695</t>
+          <t>9523</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>54706</t>
+          <t>53587</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50532</t>
+          <t>49745</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89408</t>
+          <t>92414</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39333</t>
+          <t>40313</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62854</t>
+          <t>64965</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>96109</t>
+          <t>97019</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>142595</t>
+          <t>146012</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>335</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>13599</t>
+          <t>12684</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>15484</t>
+          <t>16182</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15610</t>
+          <t>16222</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>59239</t>
+          <t>59050</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5516</t>
+          <t>5901</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16858</t>
+          <t>18269</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25051</t>
+          <t>24438</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>68110</t>
+          <t>69338</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>475175</t>
+          <t>476811</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>531747</t>
+          <t>531732</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>388911</t>
+          <t>388541</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>421264</t>
+          <t>421123</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>876427</t>
+          <t>875821</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>943613</t>
+          <t>943328</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,24%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41907</t>
+          <t>41372</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>75607</t>
+          <t>75393</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>35358</t>
+          <t>35244</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>56625</t>
+          <t>56896</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>83895</t>
+          <t>83630</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>123216</t>
+          <t>123303</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17795</t>
+          <t>17957</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>43730</t>
+          <t>43038</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>37383</t>
+          <t>38415</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>76717</t>
+          <t>76591</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>64186</t>
+          <t>66353</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>108953</t>
+          <t>108974</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>7608</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7030</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>10980</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>23770</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>36997</t>
+          <t>37760</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>18951</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>50734</t>
+          <t>49973</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>243280</t>
+          <t>245183</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>277380</t>
+          <t>277378</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>404706</t>
+          <t>406502</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>476731</t>
+          <t>477309</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>662204</t>
+          <t>666312</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>743352</t>
+          <t>746682</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,62%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>15647</t>
+          <t>15573</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>38103</t>
+          <t>37906</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>32691</t>
+          <t>33470</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>64143</t>
+          <t>65242</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,42 +3960,42 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
+          <t>5,95%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>11,61%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>73728</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>52004</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>93019</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>8,26%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
           <t>5,82%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>11,41%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>73728</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>53796</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>93053</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>8895</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>39223</t>
+          <t>39132</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>21236</t>
+          <t>21326</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>44513</t>
+          <t>44942</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>34721</t>
+          <t>35785</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>74750</t>
+          <t>74883</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4291</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7981</t>
+          <t>7730</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7564</t>
+          <t>8090</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4291</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>7511</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>17602</t>
+          <t>17627</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>7070</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>16783</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>158029</t>
+          <t>154449</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>195995</t>
+          <t>194745</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>305595</t>
+          <t>306089</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>337552</t>
+          <t>337994</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>472445</t>
+          <t>474930</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>523882</t>
+          <t>525420</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,71%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5165</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>32703</t>
+          <t>34127</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>19592</t>
+          <t>20317</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>41171</t>
+          <t>41535</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>30140</t>
+          <t>29184</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>63347</t>
+          <t>63745</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>217655</t>
+          <t>214778</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1018580</t>
+          <t>1028303</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>179962</t>
+          <t>183863</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>239273</t>
+          <t>240486</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>423485</t>
+          <t>420509</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1475122</t>
+          <t>1343263</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>30,32%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>12804</t>
+          <t>13438</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>12621</t>
+          <t>12503</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>27758</t>
+          <t>27478</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>16765</t>
+          <t>17168</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>34696</t>
+          <t>35028</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>49136</t>
+          <t>48931</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>102249</t>
+          <t>104984</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>45323</t>
+          <t>44511</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>77936</t>
+          <t>78601</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>99609</t>
+          <t>98498</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>161211</t>
+          <t>163171</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1122478</t>
+          <t>1118343</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1836855</t>
+          <t>1839822</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1618238</t>
+          <t>1621699</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1712966</t>
+          <t>1716486</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2574110</t>
+          <t>2690682</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3502054</t>
+          <t>3506213</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,14%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>109168</t>
+          <t>111700</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>195532</t>
+          <t>195707</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>142201</t>
+          <t>141537</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>193741</t>
+          <t>189590</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>265779</t>
+          <t>270003</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>369063</t>
+          <t>372592</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P37B_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P37B_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>34701</t>
+          <t>40558</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24047</t>
+          <t>28380</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48450</t>
+          <t>55503</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>35465</t>
+          <t>39113</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26606</t>
+          <t>29779</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47003</t>
+          <t>50552</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>70166</t>
+          <t>79670</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56081</t>
+          <t>64519</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88022</t>
+          <t>99440</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -873,22 +873,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>583</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>5097</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,22 +908,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>576</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>5732</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16607</t>
+          <t>20307</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10163</t>
+          <t>12759</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27187</t>
+          <t>31295</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9397</t>
+          <t>10899</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15377</t>
+          <t>17468</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>26004</t>
+          <t>31206</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18422</t>
+          <t>22232</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36979</t>
+          <t>42619</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>238194</t>
+          <t>256157</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>221731</t>
+          <t>237576</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>252575</t>
+          <t>271752</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>215016</t>
+          <t>231086</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>202774</t>
+          <t>216208</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>226824</t>
+          <t>242724</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>453210</t>
+          <t>487243</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>430389</t>
+          <t>464286</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>471279</t>
+          <t>506599</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>79,07%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>18879</t>
+          <t>20670</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11408</t>
+          <t>13369</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>34444</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>18099</t>
+          <t>20014</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12549</t>
+          <t>13937</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25528</t>
+          <t>28447</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>36978</t>
+          <t>40684</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27849</t>
+          <t>30218</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>49724</t>
+          <t>54648</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>308380</t>
+          <t>337692</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>308380</t>
+          <t>337692</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>308380</t>
+          <t>337692</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>279698</t>
+          <t>303032</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>279698</t>
+          <t>303032</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>279698</t>
+          <t>303032</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>588078</t>
+          <t>640724</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>588078</t>
+          <t>640724</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>588078</t>
+          <t>640724</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26115</t>
+          <t>29418</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16594</t>
+          <t>19573</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38668</t>
+          <t>42670</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23336</t>
+          <t>26747</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16631</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32572</t>
+          <t>36168</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>49451</t>
+          <t>56165</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37674</t>
+          <t>42724</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65694</t>
+          <t>72387</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>994</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6557</t>
+          <t>7098</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>892</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6891</t>
+          <t>7325</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14097</t>
+          <t>16001</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>8118</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>4178</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14527</t>
+          <t>15624</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,17 +1703,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>14178</t>
+          <t>15443</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8539</t>
+          <t>9067</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23722</t>
+          <t>25537</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>217696</t>
+          <t>231798</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>202211</t>
+          <t>215623</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>231401</t>
+          <t>246434</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>210221</t>
+          <t>231793</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>197780</t>
+          <t>219619</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>218591</t>
+          <t>241635</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>427918</t>
+          <t>463591</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>411016</t>
+          <t>443020</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>446105</t>
+          <t>483646</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,06%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>25294</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17132</t>
+          <t>16504</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>36724</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16369</t>
+          <t>18299</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10691</t>
+          <t>11925</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23440</t>
+          <t>25125</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>41663</t>
+          <t>44202</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31682</t>
+          <t>33043</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55473</t>
+          <t>56671</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275996</t>
+          <t>294444</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275996</t>
+          <t>294444</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275996</t>
+          <t>294444</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>260004</t>
+          <t>287868</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>260004</t>
+          <t>287868</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>260004</t>
+          <t>287868</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>536000</t>
+          <t>582312</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>536000</t>
+          <t>582312</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>536000</t>
+          <t>582312</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>269444</t>
+          <t>31101</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39189</t>
+          <t>20526</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>437753</t>
+          <t>45091</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11207</t>
+          <t>12347</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>7882</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17316</t>
+          <t>18792</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>280651</t>
+          <t>43448</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54467</t>
+          <t>32027</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>503900</t>
+          <t>58515</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -2202,67 +2202,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>854</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8467</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1396</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8971</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>4702</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1287</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>4729</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>1423</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>9569</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5065</t>
+          <t>8588</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>3834</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13462</t>
+          <t>18427</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,22 +2350,22 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3979</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9072</t>
+          <t>11427</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>9044</t>
+          <t>12800</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>6204</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18914</t>
+          <t>23314</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>1,45%</t>
         </is>
       </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>228815</t>
+          <t>251834</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>81064</t>
+          <t>234204</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>435551</t>
+          <t>266269</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>72451</t>
+          <t>82912</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>64460</t>
+          <t>73836</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79112</t>
+          <t>89653</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>301266</t>
+          <t>334746</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>103912</t>
+          <t>315663</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>501982</t>
+          <t>351728</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>82,19%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>22284</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>14480</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43923</t>
+          <t>34021</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>10440</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5444</t>
+          <t>6184</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14483</t>
+          <t>16233</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>29561</t>
+          <t>32724</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>22691</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>53587</t>
+          <t>45753</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>526198</t>
+          <t>316657</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>526198</t>
+          <t>316657</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>526198</t>
+          <t>316657</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>98405</t>
+          <t>111308</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>98405</t>
+          <t>111308</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>98405</t>
+          <t>111308</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>624603</t>
+          <t>427965</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>624603</t>
+          <t>427965</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>624603</t>
+          <t>427965</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>68026</t>
+          <t>70690</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49745</t>
+          <t>52836</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>92414</t>
+          <t>93587</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>49692</t>
+          <t>56809</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40313</t>
+          <t>44670</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64965</t>
+          <t>70852</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>117719</t>
+          <t>127499</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>97019</t>
+          <t>103397</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>146012</t>
+          <t>152346</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>18026</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12684</t>
+          <t>12441</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7358</t>
+          <t>12108</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>6183</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>16182</t>
+          <t>24704</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>27875</t>
+          <t>25654</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16222</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>59050</t>
+          <t>38445</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10094</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>6493</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18269</t>
+          <t>19255</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>37969</t>
+          <t>36948</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>24438</t>
+          <t>26467</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>69338</t>
+          <t>51689</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>505631</t>
+          <t>560324</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>476811</t>
+          <t>532942</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>531732</t>
+          <t>586773</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,22 +3145,22 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>405477</t>
+          <t>454459</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>388541</t>
+          <t>436631</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>421123</t>
+          <t>471647</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>911108</t>
+          <t>1014782</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>875821</t>
+          <t>980184</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>943328</t>
+          <t>1043368</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,04%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>55942</t>
+          <t>60448</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41372</t>
+          <t>46255</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>75393</t>
+          <t>79527</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>45574</t>
+          <t>51737</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>35244</t>
+          <t>40690</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>56896</t>
+          <t>64377</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>101516</t>
+          <t>112186</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>83630</t>
+          <t>93706</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>123303</t>
+          <t>133008</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>659413</t>
+          <t>723347</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>659413</t>
+          <t>723347</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>659413</t>
+          <t>723347</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>516257</t>
+          <t>580175</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>516257</t>
+          <t>580175</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>516257</t>
+          <t>580175</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1175670</t>
+          <t>1303522</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1175670</t>
+          <t>1303522</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1175670</t>
+          <t>1303522</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>27934</t>
+          <t>30285</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17957</t>
+          <t>19262</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>43038</t>
+          <t>45253</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>59110</t>
+          <t>66355</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>38415</t>
+          <t>54495</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>76591</t>
+          <t>80686</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>87044</t>
+          <t>96640</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>66353</t>
+          <t>80002</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>108974</t>
+          <t>117059</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1458</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3576,12 +3576,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>16985</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>8327</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11038</t>
+          <t>21437</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>14752</t>
+          <t>19132</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8563</t>
+          <t>11442</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>23770</t>
+          <t>30122</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>14701</t>
+          <t>11315</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6926</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>37760</t>
+          <t>18493</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>29453</t>
+          <t>30446</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>20752</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>49973</t>
+          <t>42818</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>262304</t>
+          <t>332014</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>245183</t>
+          <t>311203</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>277378</t>
+          <t>350308</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>435320</t>
+          <t>389319</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>406502</t>
+          <t>371559</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>477309</t>
+          <t>405906</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>697623</t>
+          <t>721333</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>666312</t>
+          <t>694178</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>746682</t>
+          <t>745502</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>79,64%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>24382</t>
+          <t>25500</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>15573</t>
+          <t>16360</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>37906</t>
+          <t>38415</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>49345</t>
+          <t>53831</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>33470</t>
+          <t>42109</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>65242</t>
+          <t>67655</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>73728</t>
+          <t>79331</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>52004</t>
+          <t>65682</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>93019</t>
+          <t>97295</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>330830</t>
+          <t>411372</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>330830</t>
+          <t>411372</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>330830</t>
+          <t>411372</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>562078</t>
+          <t>524705</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>562078</t>
+          <t>524705</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>562078</t>
+          <t>524705</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>892908</t>
+          <t>936077</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>892908</t>
+          <t>936077</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>892908</t>
+          <t>936077</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>21176</t>
+          <t>20882</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8895</t>
+          <t>8915</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>39132</t>
+          <t>38042</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>31148</t>
+          <t>37348</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>21326</t>
+          <t>24718</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>44942</t>
+          <t>52954</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>52325</t>
+          <t>58230</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>35785</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>74883</t>
+          <t>82532</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3801</t>
+          <t>4621</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7730</t>
+          <t>9188</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>3801</t>
+          <t>4621</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>8090</t>
+          <t>9128</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>11365</t>
+          <t>12657</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>7511</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>17627</t>
+          <t>18824</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>11365</t>
+          <t>12657</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>7494</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>16783</t>
+          <t>18493</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>179039</t>
+          <t>179254</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>154449</t>
+          <t>159133</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>194745</t>
+          <t>194404</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>323349</t>
+          <t>366895</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>306089</t>
+          <t>347482</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>337994</t>
+          <t>384195</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>502388</t>
+          <t>546148</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>474930</t>
+          <t>517802</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>525420</t>
+          <t>570478</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,5%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>14722</t>
+          <t>13615</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>5165</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>34127</t>
+          <t>30394</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>28384</t>
+          <t>31953</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>20317</t>
+          <t>22657</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>41535</t>
+          <t>45287</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>43106</t>
+          <t>45568</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>29184</t>
+          <t>31617</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>63745</t>
+          <t>63809</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>214938</t>
+          <t>213750</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>214938</t>
+          <t>213750</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>214938</t>
+          <t>213750</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>398047</t>
+          <t>453474</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>398047</t>
+          <t>453474</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>398047</t>
+          <t>453474</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>612985</t>
+          <t>667223</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>612985</t>
+          <t>667223</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>612985</t>
+          <t>667223</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>447396</t>
+          <t>222933</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>214778</t>
+          <t>193202</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1028303</t>
+          <t>258449</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>209960</t>
+          <t>238720</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>183863</t>
+          <t>213570</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>240486</t>
+          <t>266976</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>657355</t>
+          <t>461652</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>420509</t>
+          <t>418486</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1343263</t>
+          <t>504198</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>13523</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>5751</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>13438</t>
+          <t>27632</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>18620</t>
+          <t>20611</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>12503</t>
+          <t>14106</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>27478</t>
+          <t>28836</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>24811</t>
+          <t>34134</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>17168</t>
+          <t>23841</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>35028</t>
+          <t>50207</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>71190</t>
+          <t>81006</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>48931</t>
+          <t>63858</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>104984</t>
+          <t>102486</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>56824</t>
+          <t>58494</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>44511</t>
+          <t>46511</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>78601</t>
+          <t>73473</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>128014</t>
+          <t>139500</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>98498</t>
+          <t>117000</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>163171</t>
+          <t>163675</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1631677</t>
+          <t>1811381</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1118343</t>
+          <t>1763483</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1839822</t>
+          <t>1853821</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>1661835</t>
+          <t>1756463</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1621699</t>
+          <t>1721152</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1716486</t>
+          <t>1792657</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>3293512</t>
+          <t>3567843</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2690682</t>
+          <t>3510294</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3506213</t>
+          <t>3624814</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,53%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>159300</t>
+          <t>168420</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>111700</t>
+          <t>143591</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>195707</t>
+          <t>197147</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>167252</t>
+          <t>186274</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>141537</t>
+          <t>163105</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>189590</t>
+          <t>209774</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>326551</t>
+          <t>354694</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>270003</t>
+          <t>321027</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>372592</t>
+          <t>392494</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>2315754</t>
+          <t>2297262</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2315754</t>
+          <t>2297262</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2315754</t>
+          <t>2297262</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>2114490</t>
+          <t>2260562</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>2114490</t>
+          <t>2260562</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>2114490</t>
+          <t>2260562</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>4430244</t>
+          <t>4557823</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>4430244</t>
+          <t>4557823</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>4430244</t>
+          <t>4557823</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
